--- a/HUMB3008_Submissions.xlsx
+++ b/HUMB3008_Submissions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://curtin-my.sharepoint.com/personal/279437g_curtin_edu_au/Documents/HUMB3008 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{18AFECC2-8D3D-43AE-A6F4-EB670B073685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55E385F7-A702-4C3B-83BD-8E0E46C1C2E0}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{18AFECC2-8D3D-43AE-A6F4-EB670B073685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFF137B7-28C6-41D8-8B97-BB36A808FF86}"/>
   <bookViews>
     <workbookView xWindow="2940" yWindow="1950" windowWidth="21600" windowHeight="12645" xr2:uid="{B9BE42AF-648C-4154-85B4-97B4AAAFA346}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>studentName</t>
   </si>
@@ -60,6 +60,36 @@
   </si>
   <si>
     <t>timestamp</t>
+  </si>
+  <si>
+    <t>Daniel Brown</t>
+  </si>
+  <si>
+    <t>Amplifiers, Filters &amp; Data Acquisition</t>
+  </si>
+  <si>
+    <t>The student engaged with a clinical scenario involving EEG recording contaminated by 50 Hz mains interference and critically evaluated the blanket application of notch filtering as a solution. The tutor prompted the student to consider the potential consequences of frequency-domain filtering, specifically what clinically relevant brain activity might be obscured by removing a narrow band around 50 Hz and how notch filters alter signal integrity near the target frequency. While the student's initial reaction to the scenario was not provided in the transcript, the dialogue was designed to develop their understanding of the trade-offs between noise removal and information preservation in clinical neurophysiology, encouraging them to think beyond simple technical fixes to consider the broader implications for clinical decision-making.</t>
+  </si>
+  <si>
+    <t>dggwrgs</t>
+  </si>
+  <si>
+    <t>2026-04-21T06:03:38.834Z</t>
+  </si>
+  <si>
+    <t>q35635</t>
+  </si>
+  <si>
+    <t>Bioelectrical Signals &amp; Extracellular Fields</t>
+  </si>
+  <si>
+    <t>The student engaged with a foundational topic in clinical neurophysiology concerning how bioelectrical signals generated at the axon membrane propagate as detectable fields in the extracellular space. When prompted to explain the mechanism by which an action potential creates a voltage deflection detectable at skin surface electrodes, the student initially provided an unclear response, which the tutor reframed into a more accessible scaffolded question about the fundamental relationship between moving ions and electrical fields. The tutor guided the student toward recognizing that ion movement (specifically Na⁺ and K⁺ during an action potential) constitutes charge movement, which is the basic physical principle underlying bioelectrical signal generation. At the conclusion of this session segment, the student had not yet articulated a complete conceptual chain linking membrane ion currents to detectable extracellular electrical fields, but the tutor had established a clear foundational stepping stone for further exploration.</t>
+  </si>
+  <si>
+    <t>testttttt</t>
+  </si>
+  <si>
+    <t>2026-04-21T06:05:45.114Z</t>
   </si>
 </sst>
 </file>
@@ -122,8 +152,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EC3B72A2-96EF-4C54-92F4-04494C53D0EF}" name="Table1" displayName="Table1" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{EC3B72A2-96EF-4C54-92F4-04494C53D0EF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EC3B72A2-96EF-4C54-92F4-04494C53D0EF}" name="Table1" displayName="Table1" ref="A1:H3" totalsRowShown="0">
+  <autoFilter ref="A1:H3" xr:uid="{EC3B72A2-96EF-4C54-92F4-04494C53D0EF}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{56657A73-366D-4925-B328-54E30BE31495}" name="studentName"/>
     <tableColumn id="2" xr3:uid="{613031CB-6E8D-42EF-A1FF-19B4CB3FDEBF}" name="studentID"/>
@@ -455,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC80F58F-687C-4C42-8AF8-3274183C7F8F}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -492,6 +522,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" ht="15.75">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>3426356</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/HUMB3008_Submissions.xlsx
+++ b/HUMB3008_Submissions.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://curtin-my.sharepoint.com/personal/279437g_curtin_edu_au/Documents/HUMB3008 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://curtin-my.sharepoint.com/personal/279437g_curtin_edu_au/Documents/Documents/GitHub/humb3008-tutor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{18AFECC2-8D3D-43AE-A6F4-EB670B073685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFF137B7-28C6-41D8-8B97-BB36A808FF86}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{18AFECC2-8D3D-43AE-A6F4-EB670B073685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1466618-90D2-4C57-AB2C-7D61ECE154BA}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="1950" windowWidth="21600" windowHeight="12645" xr2:uid="{B9BE42AF-648C-4154-85B4-97B4AAAFA346}"/>
+    <workbookView xWindow="30990" yWindow="3000" windowWidth="21600" windowHeight="12645" xr2:uid="{B9BE42AF-648C-4154-85B4-97B4AAAFA346}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -96,7 +97,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +150,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,8 +490,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC80F58F-687C-4C42-8AF8-3274183C7F8F}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -496,7 +501,7 @@
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +527,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75">
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -548,7 +553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75">
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -572,6 +577,18 @@
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K16">
+        <f>5/2</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <f>2/5</f>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
